--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -1161,7 +1161,7 @@
         <v>778889</v>
       </c>
       <c r="R6" t="n">
-        <v>7251726</v>
+        <v>7251725</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187432</v>
+        <v>130187412</v>
       </c>
       <c r="B10" t="n">
-        <v>79685</v>
+        <v>92923</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>778889</v>
+        <v>778551</v>
       </c>
       <c r="R10" t="n">
-        <v>7251726</v>
+        <v>7251834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187412</v>
+        <v>130187432</v>
       </c>
       <c r="B11" t="n">
-        <v>92921</v>
+        <v>79685</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778551</v>
+        <v>778889</v>
       </c>
       <c r="R11" t="n">
-        <v>7251834</v>
+        <v>7251725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -790,7 +790,7 @@
         <v>130187421</v>
       </c>
       <c r="B3" t="n">
-        <v>57738</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187435</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>79770</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1014,7 +1014,7 @@
         <v>130187423</v>
       </c>
       <c r="B5" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>130187433</v>
       </c>
       <c r="B6" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>130187436</v>
       </c>
       <c r="B7" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130187418</v>
       </c>
       <c r="B8" t="n">
-        <v>79714</v>
+        <v>79799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130187414</v>
       </c>
       <c r="B9" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187412</v>
+        <v>130187432</v>
       </c>
       <c r="B10" t="n">
-        <v>92923</v>
+        <v>79770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>778551</v>
+        <v>778889</v>
       </c>
       <c r="R10" t="n">
-        <v>7251834</v>
+        <v>7251725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187432</v>
+        <v>130187412</v>
       </c>
       <c r="B11" t="n">
-        <v>79685</v>
+        <v>93010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778889</v>
+        <v>778551</v>
       </c>
       <c r="R11" t="n">
-        <v>7251725</v>
+        <v>7251834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1798,7 +1798,7 @@
         <v>130187413</v>
       </c>
       <c r="B12" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130187431</v>
       </c>
       <c r="B13" t="n">
-        <v>78498</v>
+        <v>78583</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187421</v>
+        <v>130187419</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>8440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778651</v>
+        <v>778633</v>
       </c>
       <c r="R2" t="n">
-        <v>7251805</v>
+        <v>7251775</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187419</v>
+        <v>130187421</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778633</v>
+        <v>778651</v>
       </c>
       <c r="R3" t="n">
-        <v>7251775</v>
+        <v>7251805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187412</v>
+        <v>130187432</v>
       </c>
       <c r="B10" t="n">
-        <v>93010</v>
+        <v>79770</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>778551</v>
+        <v>778889</v>
       </c>
       <c r="R10" t="n">
-        <v>7251834</v>
+        <v>7251725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187432</v>
+        <v>130187412</v>
       </c>
       <c r="B11" t="n">
-        <v>79770</v>
+        <v>93010</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778889</v>
+        <v>778551</v>
       </c>
       <c r="R11" t="n">
-        <v>7251725</v>
+        <v>7251834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187419</v>
+        <v>130187421</v>
       </c>
       <c r="B2" t="n">
-        <v>8440</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778633</v>
+        <v>778651</v>
       </c>
       <c r="R2" t="n">
-        <v>7251775</v>
+        <v>7251805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187421</v>
+        <v>130187419</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>8440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778651</v>
+        <v>778633</v>
       </c>
       <c r="R3" t="n">
-        <v>7251805</v>
+        <v>7251775</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187421</v>
+        <v>130187419</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>8440</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778651</v>
+        <v>778633</v>
       </c>
       <c r="R2" t="n">
-        <v>7251805</v>
+        <v>7251775</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187419</v>
+        <v>130187421</v>
       </c>
       <c r="B3" t="n">
-        <v>8440</v>
+        <v>57823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778633</v>
+        <v>778651</v>
       </c>
       <c r="R3" t="n">
-        <v>7251775</v>
+        <v>7251805</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130187419</v>
+        <v>130187421</v>
       </c>
       <c r="B2" t="n">
-        <v>8440</v>
+        <v>57823</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>106554</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>778633</v>
+        <v>778651</v>
       </c>
       <c r="R2" t="n">
-        <v>7251775</v>
+        <v>7251805</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,32 +787,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130187421</v>
+        <v>130187419</v>
       </c>
       <c r="B3" t="n">
-        <v>57823</v>
+        <v>8440</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106554</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Björksplintborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Scolytus ratzeburgii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Janson, 1856</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>778651</v>
+        <v>778633</v>
       </c>
       <c r="R3" t="n">
-        <v>7251805</v>
+        <v>7251775</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -902,7 +902,7 @@
         <v>130187435</v>
       </c>
       <c r="B4" t="n">
-        <v>79770</v>
+        <v>79773</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187436</v>
+        <v>130187423</v>
       </c>
       <c r="B5" t="n">
-        <v>78583</v>
+        <v>79802</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>779068</v>
+        <v>778658</v>
       </c>
       <c r="R5" t="n">
-        <v>7251575</v>
+        <v>7251802</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1126,7 +1126,7 @@
         <v>130187433</v>
       </c>
       <c r="B6" t="n">
-        <v>78583</v>
+        <v>78586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187423</v>
+        <v>130187436</v>
       </c>
       <c r="B7" t="n">
-        <v>79799</v>
+        <v>78586</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>778658</v>
+        <v>779068</v>
       </c>
       <c r="R7" t="n">
-        <v>7251802</v>
+        <v>7251575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1350,7 +1350,7 @@
         <v>130187418</v>
       </c>
       <c r="B8" t="n">
-        <v>79799</v>
+        <v>79802</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130187414</v>
       </c>
       <c r="B9" t="n">
-        <v>78583</v>
+        <v>78586</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187432</v>
+        <v>130187412</v>
       </c>
       <c r="B10" t="n">
-        <v>79770</v>
+        <v>93013</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>778889</v>
+        <v>778551</v>
       </c>
       <c r="R10" t="n">
-        <v>7251725</v>
+        <v>7251834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187412</v>
+        <v>130187432</v>
       </c>
       <c r="B11" t="n">
-        <v>93010</v>
+        <v>79773</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778551</v>
+        <v>778889</v>
       </c>
       <c r="R11" t="n">
-        <v>7251834</v>
+        <v>7251725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
@@ -1798,7 +1798,7 @@
         <v>130187413</v>
       </c>
       <c r="B12" t="n">
-        <v>78583</v>
+        <v>78586</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130187431</v>
       </c>
       <c r="B13" t="n">
-        <v>78583</v>
+        <v>78586</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187421</v>
       </c>
       <c r="B2" t="n">
-        <v>57823</v>
+        <v>57849</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187435</v>
       </c>
       <c r="B4" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187423</v>
+        <v>130187433</v>
       </c>
       <c r="B5" t="n">
-        <v>79802</v>
+        <v>78612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778658</v>
+        <v>778889</v>
       </c>
       <c r="R5" t="n">
-        <v>7251802</v>
+        <v>7251725</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187433</v>
+        <v>130187423</v>
       </c>
       <c r="B6" t="n">
-        <v>78586</v>
+        <v>79828</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778889</v>
+        <v>778658</v>
       </c>
       <c r="R6" t="n">
-        <v>7251725</v>
+        <v>7251802</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1238,7 +1238,7 @@
         <v>130187436</v>
       </c>
       <c r="B7" t="n">
-        <v>78586</v>
+        <v>78612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>130187418</v>
       </c>
       <c r="B8" t="n">
-        <v>79802</v>
+        <v>79828</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130187414</v>
       </c>
       <c r="B9" t="n">
-        <v>78586</v>
+        <v>78612</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>130187412</v>
       </c>
       <c r="B10" t="n">
-        <v>93013</v>
+        <v>93039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130187432</v>
       </c>
       <c r="B11" t="n">
-        <v>79773</v>
+        <v>79799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130187413</v>
       </c>
       <c r="B12" t="n">
-        <v>78586</v>
+        <v>78612</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130187431</v>
       </c>
       <c r="B13" t="n">
-        <v>78586</v>
+        <v>78612</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187423</v>
+        <v>130187436</v>
       </c>
       <c r="B6" t="n">
-        <v>79828</v>
+        <v>78612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1134,21 +1134,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>778658</v>
+        <v>779068</v>
       </c>
       <c r="R6" t="n">
-        <v>7251802</v>
+        <v>7251575</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187436</v>
+        <v>130187423</v>
       </c>
       <c r="B7" t="n">
-        <v>78612</v>
+        <v>79828</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>779068</v>
+        <v>778658</v>
       </c>
       <c r="R7" t="n">
-        <v>7251575</v>
+        <v>7251802</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187412</v>
+        <v>130187432</v>
       </c>
       <c r="B10" t="n">
-        <v>93039</v>
+        <v>79799</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>778551</v>
+        <v>778889</v>
       </c>
       <c r="R10" t="n">
-        <v>7251834</v>
+        <v>7251725</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187432</v>
+        <v>130187412</v>
       </c>
       <c r="B11" t="n">
-        <v>79799</v>
+        <v>93040</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778889</v>
+        <v>778551</v>
       </c>
       <c r="R11" t="n">
-        <v>7251725</v>
+        <v>7251834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -1571,32 +1571,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>130187432</v>
+        <v>130187412</v>
       </c>
       <c r="B10" t="n">
-        <v>79799</v>
+        <v>93041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>229821</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1606,10 +1606,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>778889</v>
+        <v>778551</v>
       </c>
       <c r="R10" t="n">
-        <v>7251725</v>
+        <v>7251834</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1641,7 +1641,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
@@ -1683,32 +1683,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>130187412</v>
+        <v>130187432</v>
       </c>
       <c r="B11" t="n">
-        <v>93040</v>
+        <v>79799</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>229821</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1718,10 +1718,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>778551</v>
+        <v>778889</v>
       </c>
       <c r="R11" t="n">
-        <v>7251834</v>
+        <v>7251725</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1753,7 +1753,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130187421</v>
       </c>
       <c r="B2" t="n">
-        <v>57849</v>
+        <v>57851</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>130187435</v>
       </c>
       <c r="B4" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>130187433</v>
+        <v>130187423</v>
       </c>
       <c r="B5" t="n">
-        <v>78612</v>
+        <v>79830</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1022,21 +1022,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6437</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1046,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>778889</v>
+        <v>778658</v>
       </c>
       <c r="R5" t="n">
-        <v>7251725</v>
+        <v>7251802</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1081,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:17</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>130187436</v>
+        <v>130187433</v>
       </c>
       <c r="B6" t="n">
-        <v>78612</v>
+        <v>78614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>779068</v>
+        <v>778889</v>
       </c>
       <c r="R6" t="n">
-        <v>7251575</v>
+        <v>7251725</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1193,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>130187423</v>
+        <v>130187436</v>
       </c>
       <c r="B7" t="n">
-        <v>79828</v>
+        <v>78614</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1246,21 +1246,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>6437</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1270,10 +1270,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>778658</v>
+        <v>779068</v>
       </c>
       <c r="R7" t="n">
-        <v>7251802</v>
+        <v>7251575</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1315,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
@@ -1350,7 +1350,7 @@
         <v>130187418</v>
       </c>
       <c r="B8" t="n">
-        <v>79828</v>
+        <v>79830</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>130187414</v>
       </c>
       <c r="B9" t="n">
-        <v>78612</v>
+        <v>78614</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1574,7 +1574,7 @@
         <v>130187412</v>
       </c>
       <c r="B10" t="n">
-        <v>93041</v>
+        <v>93043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1686,7 +1686,7 @@
         <v>130187432</v>
       </c>
       <c r="B11" t="n">
-        <v>79799</v>
+        <v>79801</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         <v>130187413</v>
       </c>
       <c r="B12" t="n">
-        <v>78612</v>
+        <v>78614</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1910,7 +1910,7 @@
         <v>130187431</v>
       </c>
       <c r="B13" t="n">
-        <v>78612</v>
+        <v>78614</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -1574,7 +1574,7 @@
         <v>130187412</v>
       </c>
       <c r="B10" t="n">
-        <v>93043</v>
+        <v>93047</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 53100-2025 artfynd.xlsx
+++ b/artfynd/A 53100-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2017,6 +2017,118 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>133646161</v>
+      </c>
+      <c r="B14" t="n">
+        <v>57869</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>100011</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Kungsörn</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Aquila chrysaetos</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Blåsmark, Nb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>780001</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7251908</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Piteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Piteå socken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-03-04</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:59</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Via Elin Lindmark</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
